--- a/floristics_data/transects/transect_data.xlsx
+++ b/floristics_data/transects/transect_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwenr\Documents\Git\junction_floristics\floristics_data\transects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3882EE46-4BA7-4205-BB43-810830FCA6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564E36D1-8751-46EF-8CBA-93E0DE6C43CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{850DE120-91C1-49E5-8364-4BA7F4010141}"/>
   </bookViews>
@@ -566,7 +566,7 @@
     <col min="4" max="4" width="15.15625" customWidth="1"/>
     <col min="5" max="5" width="16.3671875" customWidth="1"/>
     <col min="6" max="6" width="14.15625" customWidth="1"/>
-    <col min="7" max="7" width="40.26171875" customWidth="1"/>
+    <col min="7" max="7" width="40.578125" customWidth="1"/>
     <col min="8" max="9" width="12.89453125" customWidth="1"/>
     <col min="10" max="11" width="13.05078125" customWidth="1"/>
     <col min="12" max="12" width="10.1015625" customWidth="1"/>
@@ -596,25 +596,25 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
@@ -655,13 +655,13 @@
         <v>59</v>
       </c>
       <c r="L2">
-        <v>2.286</v>
+        <v>2.27</v>
       </c>
       <c r="M2">
+        <v>2.5609999999999999</v>
+      </c>
+      <c r="N2">
         <v>1.98</v>
-      </c>
-      <c r="N2">
-        <v>2.5920000000000001</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>19</v>
@@ -702,13 +702,13 @@
         <v>59</v>
       </c>
       <c r="L3">
-        <v>1.331</v>
+        <v>1.1910000000000001</v>
       </c>
       <c r="M3">
         <v>0.68700000000000006</v>
       </c>
       <c r="N3">
-        <v>1.9750000000000001</v>
+        <v>1.696</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -746,7 +746,7 @@
         <v>59</v>
       </c>
       <c r="L4">
-        <v>1.6220000000000001</v>
+        <v>1.621</v>
       </c>
       <c r="M4">
         <v>1.8140000000000001</v>
@@ -984,7 +984,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" ht="316.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>-99.781052000000003</v>
       </c>
       <c r="L11">
-        <v>1.907</v>
+        <v>1.9059999999999999</v>
       </c>
       <c r="M11">
         <v>1.85</v>
@@ -1075,7 +1075,7 @@
         <v>1.9630000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1116,10 +1116,10 @@
         <v>1.522</v>
       </c>
       <c r="N12">
-        <v>1.1399999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>1.139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>56</v>
       </c>

--- a/floristics_data/transects/transect_data.xlsx
+++ b/floristics_data/transects/transect_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwenr\Documents\Git\junction_floristics\floristics_data\transects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564E36D1-8751-46EF-8CBA-93E0DE6C43CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86F4619-D781-483F-8804-C698431DAC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{850DE120-91C1-49E5-8364-4BA7F4010141}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="64">
   <si>
     <t>transect_name</t>
   </si>
@@ -95,9 +95,6 @@
     <t>90 degrees E</t>
   </si>
   <si>
-    <t>Oak/juniper woodland with sparsegrass, limestone rocky slope, east of wash. Open at quadrats.</t>
-  </si>
-  <si>
     <t>West canyon loop trail haphazard - WCL1 on GPS, Dermatophyllum secundiflorum</t>
   </si>
   <si>
@@ -110,18 +107,12 @@
     <t>356 degrees N</t>
   </si>
   <si>
-    <t>Wayside begins at the bottom of a wash. Ascends up slope at a slight angle. Primary cover is Juniper and Quercus (red oak?). Silty loam with small pieces of limestone throughout matrix. Large limestones all throughout slope. Partial to full shade throughout.</t>
-  </si>
-  <si>
     <t>slr_6</t>
   </si>
   <si>
     <t>151 degrees SE</t>
   </si>
   <si>
-    <t>Rocky, grass and bareground herbaceous layer with sparse cacti, 2-3 m tall woody layer with sparse coverage - juniper and rhus virens</t>
-  </si>
-  <si>
     <t>Bareground, rock, and litter estimates were not recorded for these quadrats</t>
   </si>
   <si>
@@ -134,27 +125,18 @@
     <t>278 degrees W</t>
   </si>
   <si>
-    <t>Intersecting rocky washes 5-6 m canopy of oak, subcanopy of juniper</t>
-  </si>
-  <si>
     <t>slr_28</t>
   </si>
   <si>
     <t>44 degrees NE</t>
   </si>
   <si>
-    <t>Alluvial terrace - canopy of oak, cedar elm, understory of mesquite, grass, Opuntia sp., lots of litter</t>
-  </si>
-  <si>
     <t>slr_54</t>
   </si>
   <si>
     <t>60 degrees NE</t>
   </si>
   <si>
-    <t xml:space="preserve">Rocky, sparse grass with yucca and cacti, 2-3 m woody layer with decent coverage - juniper, agarita. Cliff below start point  </t>
-  </si>
-  <si>
     <t>slr_368</t>
   </si>
   <si>
@@ -164,18 +146,12 @@
     <t>241 degrees SW</t>
   </si>
   <si>
-    <t>Rocky flood plain, round river rock substrate, open and scoured - mostly herbaceous (asteraceae, salvia), some mesquite, pecan, hackberry, sycamore</t>
-  </si>
-  <si>
     <t>slr_503</t>
   </si>
   <si>
     <t>89 degrees E</t>
   </si>
   <si>
-    <t>Terrace and flood plain - upbank and very close to river, pecan and sycamore grove, very grassy - lots of Ratibida and Salvia, some unhappy mesquite, Opuntia</t>
-  </si>
-  <si>
     <t>Ptelea trifoliata on transect at 46.5, past feather flower grass, grass with the big inflorescence by pond_1, Johnson grass (Sorghum halipense), Elymus_2 sp (could be same as first Elymus at pond_1)</t>
   </si>
   <si>
@@ -185,9 +161,6 @@
     <t>3.3 degrees N</t>
   </si>
   <si>
-    <t>Near bare rock, exposed bed rock on side of hill. South facing. Silty loam decomposed limestone bed rock. Full sun to partial shade. ~45 degree slope. Transect ascending uphill northward. Overlooking a wash/stream bed. Mixed shrubland. Associated species: J. asheii (many dead, some resprouting), Leucophyllum fruitescens, Euphora secundiflora, Mahonia trifoliata, bear grass (Nolina sp.), Rhus virens (less common), Diosyros texana, Forestera, condolia, stingray plant (Schwilk knows what it is)</t>
-  </si>
-  <si>
     <t>Declination = 3.30, Stameria waypoint: 30.47667, -99.79869</t>
   </si>
   <si>
@@ -197,28 +170,67 @@
     <t>157 degrees SE</t>
   </si>
   <si>
-    <t>Flood plane, very rocky (very similar to 368) - lots of grass, almost no woody species - some small mesquite, willow along the river. Dominated by glandular tooth leaf, slavia, ratibida, some opuntia</t>
-  </si>
-  <si>
     <t>ttj_8</t>
   </si>
   <si>
     <t>260 degrees W</t>
   </si>
   <si>
-    <t>Dense mesquite woodland covered in grass and justichia, some pecan trees, canopy about 4-5 m tall, associated species include white horehound, ratibida, opunita, christmas cholla, mallow?</t>
-  </si>
-  <si>
     <t>ttj_70</t>
   </si>
   <si>
     <t>103 degrees E</t>
   </si>
   <si>
-    <t>Alluvial terrace, mixed shrubs, dense grass understory, canopy of juniper, cedar elm, oak - near small wash coming down hill, abruptly slopes up after about 100 m. Some opuntia</t>
-  </si>
-  <si>
     <t>contact_author</t>
+  </si>
+  <si>
+    <t>slope_aspect</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>NES</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Rocky, sparse grass with yucca and cacti, 2-3 m woody layer with decent coverage - juniper, agarita. Cliff below start point.</t>
+  </si>
+  <si>
+    <t>Oak/juniper woodland with sparse grass, limestone rocky slope, east of wash. Open at quadrats.</t>
+  </si>
+  <si>
+    <t>Wayside begins at the bottom of a wash. Ascends up slope at a slight angle. Primary cover is juniper and Quercus sp. L. (red oak?). Silty loam with small pieces of limestone throughout matrix. Large limestones all throughout slope. Partial to full shade throughout.</t>
+  </si>
+  <si>
+    <t>Rocky, grass and bare-ground herbaceous layer with sparse cacti, 2-3 m tall woody layer with sparse coverage - juniper and Rhus virens Lindh. ex A. Gray.</t>
+  </si>
+  <si>
+    <t>Intersecting rocky washes, 5-6 m canopy of oak, subcanopy of juniper.</t>
+  </si>
+  <si>
+    <t>Alluvial terrace - canopy of oak, cedar elm, understory of mesquite, grass, Opuntia sp. Mill., lots of litter.</t>
+  </si>
+  <si>
+    <t>Rocky flood plain, round river rock substrate, open and scoured - mostly herbaceous (Asteraceae, Salvia sp. L.), some mesquite, pecan, hackberry, sycamore.</t>
+  </si>
+  <si>
+    <t>Terrace and flood plain - up bank and very close to river, pecan and sycamore grove, very grassy - lots of Ratibida sp. Raf. and Salvia sp. L., some unhappy mesquite, Opuntia sp. Mill..</t>
+  </si>
+  <si>
+    <t>Near bare rock, exposed bedrock on side of hill. South facing. Silty loam decomposed limestone bed rock. Full sun to partial shade. ~45 degree slope. Transect ascending uphill northward. Overlooking a wash/stream bed. Mixed shrubland. Associated species: J. ashei J. Buchholz (many dead, some resprouting), Leucophyllum frutescens (Berland.) I.M. Johnst., Sophora secundiflora (Ortega) Lag. ex DC., Mahonia trifoliata (Moric.) Fedde, Nolina sp. Michx., Rhus virens Lindh. ex A. Gray (less common), Diospyros texana Scheele, Forestiera sp. Poir., Condalia sp. Cav., Guaiacum angustifolium Engelm..</t>
+  </si>
+  <si>
+    <t>Flood plain, very rocky (very similar to 368) - lots of grass, almost no woody species - some small mesquite, willow along the river. Dominated by Brickellia dentata (DC.) Sch. Bip., Salvia sp. L., Ratibida sp Raf., and some Opuntia sp. Mill..</t>
+  </si>
+  <si>
+    <t>Dense mesquite woodland covered in grass and Justicia sp. L., some pecan trees, canopy about 4-5 m tall, associated species include white horehound, Ratibida sp. Raf., Opuntia sp. Mill., christmas cholla, mallow.</t>
+  </si>
+  <si>
+    <t>Alluvial terrace, mixed shrubs, dense grass understory, canopy of juniper, cedar elm, oak - near small wash coming down hill, abruptly slopes up after about 100 m. Some Opuntia sp. Mill..</t>
   </si>
 </sst>
 </file>
@@ -557,23 +569,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A1DA38C-2A45-45DE-85D5-EC002D6B6A7D}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="15.7890625" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="15.15625" customWidth="1"/>
-    <col min="5" max="5" width="16.3671875" customWidth="1"/>
-    <col min="6" max="6" width="14.15625" customWidth="1"/>
-    <col min="7" max="7" width="40.578125" customWidth="1"/>
-    <col min="8" max="9" width="12.89453125" customWidth="1"/>
-    <col min="10" max="11" width="13.05078125" customWidth="1"/>
-    <col min="12" max="12" width="10.1015625" customWidth="1"/>
-    <col min="15" max="15" width="26.41796875" customWidth="1"/>
+    <col min="3" max="3" width="11.9453125" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="15.15625" customWidth="1"/>
+    <col min="6" max="6" width="16.3671875" customWidth="1"/>
+    <col min="7" max="7" width="14.15625" customWidth="1"/>
+    <col min="8" max="8" width="32.41796875" customWidth="1"/>
+    <col min="9" max="10" width="12.89453125" customWidth="1"/>
+    <col min="11" max="12" width="13.05078125" customWidth="1"/>
+    <col min="13" max="13" width="10.1015625" customWidth="1"/>
+    <col min="16" max="16" width="26.41796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,585 +594,624 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2">
+        <v>45797</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2">
+        <v>2.27</v>
+      </c>
+      <c r="N2">
+        <v>2.5609999999999999</v>
+      </c>
+      <c r="O2">
+        <v>1.98</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="2">
         <v>45797</v>
       </c>
-      <c r="D2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2">
-        <v>2.27</v>
-      </c>
-      <c r="M2">
-        <v>2.5609999999999999</v>
-      </c>
-      <c r="N2">
-        <v>1.98</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>19</v>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3">
+        <v>1.1910000000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="O3">
+        <v>1.696</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45797</v>
-      </c>
-      <c r="D3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" t="s">
+    <row r="4" spans="1:16" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>22</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3">
-        <v>1.1910000000000001</v>
-      </c>
-      <c r="M3">
-        <v>0.68700000000000006</v>
-      </c>
-      <c r="N3">
-        <v>1.696</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2">
         <v>45795</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4">
+        <v>1.621</v>
+      </c>
+      <c r="N4">
+        <v>1.8140000000000001</v>
+      </c>
+      <c r="O4">
+        <v>1.429</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="2">
+        <v>45796</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="N5">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="O5">
+        <v>1.421</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2">
+        <v>45797</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
+        <v>1.492</v>
+      </c>
+      <c r="N6">
+        <v>1.3480000000000001</v>
+      </c>
+      <c r="O6">
+        <v>1.6359999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="2">
+        <v>45795</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7">
+        <v>1.5389999999999999</v>
+      </c>
+      <c r="N7">
+        <v>1.5620000000000001</v>
+      </c>
+      <c r="O7">
+        <v>1.5149999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2">
+        <v>45797</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8">
+        <v>2.339</v>
+      </c>
+      <c r="N8">
+        <v>2.2429999999999999</v>
+      </c>
+      <c r="O8">
+        <v>2.4340000000000002</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2">
+        <v>45797</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4">
-        <v>1.621</v>
-      </c>
-      <c r="M4">
-        <v>1.8140000000000001</v>
-      </c>
-      <c r="N4">
-        <v>1.429</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>27</v>
+      <c r="I9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9">
+        <v>2.2440000000000002</v>
+      </c>
+      <c r="N9">
+        <v>2.1930000000000001</v>
+      </c>
+      <c r="O9">
+        <v>2.2949999999999999</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2">
-        <v>45796</v>
-      </c>
-      <c r="D5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5">
-        <v>0.98499999999999999</v>
-      </c>
-      <c r="M5">
-        <v>0.54900000000000004</v>
-      </c>
-      <c r="N5">
-        <v>1.421</v>
+    <row r="10" spans="1:16" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2">
+        <v>45798</v>
+      </c>
+      <c r="E10">
+        <v>30.476721000000001</v>
+      </c>
+      <c r="F10">
+        <v>-99.799796999999998</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10">
+        <v>30.476849999999999</v>
+      </c>
+      <c r="J10">
+        <v>-99.799880000000002</v>
+      </c>
+      <c r="K10">
+        <v>30.476970000000001</v>
+      </c>
+      <c r="L10">
+        <v>-99.799980000000005</v>
+      </c>
+      <c r="M10">
+        <v>1.681</v>
+      </c>
+      <c r="N10">
+        <v>1.7450000000000001</v>
+      </c>
+      <c r="O10">
+        <v>1.6160000000000001</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2">
-        <v>45797</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" t="s">
+    <row r="11" spans="1:16" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6">
-        <v>1.492</v>
-      </c>
-      <c r="M6">
-        <v>1.3480000000000001</v>
-      </c>
-      <c r="N6">
-        <v>1.6359999999999999</v>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2">
+        <v>45798</v>
+      </c>
+      <c r="E11">
+        <v>30.478650999999999</v>
+      </c>
+      <c r="F11">
+        <v>-99.781181000000004</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11">
+        <v>30.47852</v>
+      </c>
+      <c r="J11">
+        <v>-99.781137000000001</v>
+      </c>
+      <c r="K11">
+        <v>30.478370000000002</v>
+      </c>
+      <c r="L11">
+        <v>-99.781052000000003</v>
+      </c>
+      <c r="M11">
+        <v>1.9059999999999999</v>
+      </c>
+      <c r="N11">
+        <v>1.85</v>
+      </c>
+      <c r="O11">
+        <v>1.9630000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2">
-        <v>45795</v>
-      </c>
-      <c r="D7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7">
-        <v>1.5389999999999999</v>
-      </c>
-      <c r="M7">
-        <v>1.5620000000000001</v>
-      </c>
-      <c r="N7">
-        <v>1.5149999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2">
-        <v>45797</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8">
-        <v>2.339</v>
-      </c>
-      <c r="M8">
-        <v>2.2429999999999999</v>
-      </c>
-      <c r="N8">
-        <v>2.4340000000000002</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2">
-        <v>45797</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" t="s">
+    <row r="12" spans="1:16" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
         <v>43</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9">
-        <v>2.2440000000000002</v>
-      </c>
-      <c r="M9">
-        <v>2.1930000000000001</v>
-      </c>
-      <c r="N9">
-        <v>2.2949999999999999</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="316.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="2">
-        <v>45798</v>
-      </c>
-      <c r="D10">
-        <v>30.476721000000001</v>
-      </c>
-      <c r="E10">
-        <v>-99.799796999999998</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10">
-        <v>30.476849999999999</v>
-      </c>
-      <c r="I10">
-        <v>-99.799880000000002</v>
-      </c>
-      <c r="J10">
-        <v>30.476970000000001</v>
-      </c>
-      <c r="K10">
-        <v>-99.799980000000005</v>
-      </c>
-      <c r="L10">
-        <v>1.681</v>
-      </c>
-      <c r="M10">
-        <v>1.7450000000000001</v>
-      </c>
-      <c r="N10">
-        <v>1.6160000000000001</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="115.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="2">
-        <v>45798</v>
-      </c>
-      <c r="D11">
-        <v>30.478650999999999</v>
-      </c>
-      <c r="E11">
-        <v>-99.781181000000004</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11">
-        <v>30.47852</v>
-      </c>
-      <c r="I11">
-        <v>-99.781137000000001</v>
-      </c>
-      <c r="J11">
-        <v>30.478370000000002</v>
-      </c>
-      <c r="K11">
-        <v>-99.781052000000003</v>
-      </c>
-      <c r="L11">
-        <v>1.9059999999999999</v>
-      </c>
-      <c r="M11">
-        <v>1.85</v>
-      </c>
-      <c r="N11">
-        <v>1.9630000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="115.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
-        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2">
         <v>45798</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>30.474886000000001</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>-99.779607999999996</v>
       </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12">
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12">
         <v>30.474893000000002</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-99.779758999999999</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>30.474945999999999</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>-99.779919000000007</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>1.331</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>1.522</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>1.139</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="2">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="2">
         <v>45798</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>30.478331000000001</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>-99.798000000000002</v>
       </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13">
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13">
         <v>30.478269000000001</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>-99.797841000000005</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>30.478256999999999</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>-99.797663999999997</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>1.966</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>1.62</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>2.3119999999999998</v>
       </c>
     </row>
